--- a/VerveStacks_NOR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5037F113-C18E-4F87-B83C-AF6B50091500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B78E602-71DA-45BC-B3B1-EE932A292510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -692,16 +692,52 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_NOR_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_NOR_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_NOR_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_solelc_spv_NOR_009</t>
@@ -722,6 +758,36 @@
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_solelc_spv_NOR_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_NOR_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_NOR_001</t>
   </si>
   <si>
@@ -740,81 +806,33 @@
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_solelc_spv_NOR_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_NOR_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Drammen_NOR</t>
+  </si>
+  <si>
     <t>e_Haugesund_NOR</t>
   </si>
   <si>
+    <t>e_Notodden_NOR</t>
+  </si>
+  <si>
+    <t>e_Skien_NOR</t>
+  </si>
+  <si>
+    <t>e_Lyngdal_NOR</t>
+  </si>
+  <si>
+    <t>e_Egersund_NOR</t>
+  </si>
+  <si>
+    <t>e_Fredrikstad_NOR</t>
+  </si>
+  <si>
     <t>e_Kristiansand_NOR</t>
   </si>
   <si>
@@ -824,6 +842,21 @@
     <t>e_Stord_NOR</t>
   </si>
   <si>
+    <t>e_Strand_NOR</t>
+  </si>
+  <si>
+    <t>e_Sarpsborg_NOR</t>
+  </si>
+  <si>
+    <t>e_Froyland_NOR</t>
+  </si>
+  <si>
+    <t>e_Oslo_NOR</t>
+  </si>
+  <si>
+    <t>e_Stavanger_NOR</t>
+  </si>
+  <si>
     <t>e_Voss_NOR</t>
   </si>
   <si>
@@ -833,37 +866,52 @@
     <t>e_Bergen_NOR</t>
   </si>
   <si>
-    <t>e_Oslo_NOR</t>
-  </si>
-  <si>
-    <t>e_Stavanger_NOR</t>
-  </si>
-  <si>
-    <t>e_Fredrikstad_NOR</t>
-  </si>
-  <si>
-    <t>e_Skien_NOR</t>
-  </si>
-  <si>
-    <t>e_Lyngdal_NOR</t>
-  </si>
-  <si>
-    <t>e_Froyland_NOR</t>
-  </si>
-  <si>
-    <t>e_Strand_NOR</t>
-  </si>
-  <si>
-    <t>e_Sarpsborg_NOR</t>
-  </si>
-  <si>
-    <t>e_Egersund_NOR</t>
-  </si>
-  <si>
-    <t>e_Drammen_NOR</t>
-  </si>
-  <si>
-    <t>e_Notodden_NOR</t>
+    <t>distr_wonelc_won_NOR_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wonelc_won_NOR_009</t>
@@ -884,16 +932,34 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_NOR_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>distr_wonelc_won_NOR_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_NOR_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_NOR_017</t>
@@ -902,70 +968,28 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_NOR_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_NOR_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
+    <t>elc_won_NOR_003</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_011</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_014</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_002</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_006</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_015</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_005</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_016</t>
   </si>
   <si>
     <t>elc_won_NOR_009</t>
@@ -977,54 +1001,198 @@
     <t>elc_won_NOR_012</t>
   </si>
   <si>
-    <t>elc_won_NOR_015</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_006</t>
+    <t>elc_won_NOR_004</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_007</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_008</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_013</t>
+  </si>
+  <si>
+    <t>elc_won_NOR_001</t>
   </si>
   <si>
     <t>elc_won_NOR_017</t>
   </si>
   <si>
-    <t>elc_won_NOR_002</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_005</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_016</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_001</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_003</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_011</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_014</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_004</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_007</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_008</t>
-  </si>
-  <si>
-    <t>elc_won_NOR_013</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_NOR_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_NOR_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_NOR_004</t>
   </si>
   <si>
@@ -1037,6 +1205,18 @@
     <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_NOR_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_NOR_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_NOR_021</t>
   </si>
   <si>
@@ -1055,192 +1235,138 @@
     <t>connecting wind offshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_NOR_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_NOR_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>elc_wof_NOR_007</t>
   </si>
   <si>
     <t>e_Kristiansund_NOR</t>
   </si>
   <si>
+    <t>elc_wof_NOR_012</t>
+  </si>
+  <si>
+    <t>e_Lindas_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_014</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_006</t>
+  </si>
+  <si>
+    <t>e_Bodo_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_016</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_008</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_010</t>
+  </si>
+  <si>
+    <t>e_Volda_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_024</t>
+  </si>
+  <si>
+    <t>e_Vadso_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_032</t>
+  </si>
+  <si>
+    <t>e_Finnsnes_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_034</t>
+  </si>
+  <si>
+    <t>e_Alta_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_003</t>
+  </si>
+  <si>
+    <t>e_Fauske_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_005</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_013</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_022</t>
+  </si>
+  <si>
+    <t>e_Namsos_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_023</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_028</t>
+  </si>
+  <si>
+    <t>e_NOR69p9N27p1E_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_011</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_019</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_001</t>
+  </si>
+  <si>
+    <t>e_Narvik_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_020</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_030</t>
+  </si>
+  <si>
+    <t>e_NOR65p0N13p2E_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_033</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_017</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_029</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_036</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_002</t>
+  </si>
+  <si>
+    <t>e_NOR68p0N16p4E_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_009</t>
+  </si>
+  <si>
+    <t>e_Alesund_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_026</t>
+  </si>
+  <si>
+    <t>e_Trondheim_NOR</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_035</t>
+  </si>
+  <si>
     <t>elc_wof_NOR_004</t>
   </si>
   <si>
@@ -1250,148 +1376,22 @@
     <t>elc_wof_NOR_027</t>
   </si>
   <si>
+    <t>elc_wof_NOR_015</t>
+  </si>
+  <si>
+    <t>elc_wof_NOR_018</t>
+  </si>
+  <si>
+    <t>e_MoIRana_NOR</t>
+  </si>
+  <si>
     <t>elc_wof_NOR_021</t>
   </si>
   <si>
     <t>elc_wof_NOR_025</t>
   </si>
   <si>
-    <t>e_Vadso_NOR</t>
-  </si>
-  <si>
     <t>elc_wof_NOR_031</t>
-  </si>
-  <si>
-    <t>e_Finnsnes_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_016</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_006</t>
-  </si>
-  <si>
-    <t>e_Bodo_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_033</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_015</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_018</t>
-  </si>
-  <si>
-    <t>e_MoIRana_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_024</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_032</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_034</t>
-  </si>
-  <si>
-    <t>e_Alta_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_012</t>
-  </si>
-  <si>
-    <t>e_Lindas_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_014</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_003</t>
-  </si>
-  <si>
-    <t>e_Fauske_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_005</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_013</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_022</t>
-  </si>
-  <si>
-    <t>e_Namsos_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_023</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_028</t>
-  </si>
-  <si>
-    <t>e_NOR69p9N27p1E_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_001</t>
-  </si>
-  <si>
-    <t>e_Narvik_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_020</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_030</t>
-  </si>
-  <si>
-    <t>e_NOR65p0N13p2E_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_017</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_029</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_036</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_002</t>
-  </si>
-  <si>
-    <t>e_NOR68p0N16p4E_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_009</t>
-  </si>
-  <si>
-    <t>e_Alesund_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_026</t>
-  </si>
-  <si>
-    <t>e_Trondheim_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_035</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_008</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_010</t>
-  </si>
-  <si>
-    <t>e_Volda_NOR</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_011</t>
-  </si>
-  <si>
-    <t>elc_wof_NOR_019</t>
   </si>
   <si>
     <t>e_won_NOR_001</t>
@@ -5456,7 +5456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B380B9-0171-48FF-930F-FA17787FD733}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{555E2C56-A90B-46E3-A598-DCF4E533D9C3}">
   <dimension ref="B9:BD46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -5694,16 +5694,16 @@
         <v>209</v>
       </c>
       <c r="Y11" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Z11" t="s">
         <v>249</v>
       </c>
       <c r="AA11">
-        <v>0.99752858704396352</v>
+        <v>0.99895498782328085</v>
       </c>
       <c r="AB11">
-        <v>45.309237527336073</v>
+        <v>19.158556573184136</v>
       </c>
       <c r="AD11" t="s">
         <v>208</v>
@@ -5733,13 +5733,13 @@
         <v>301</v>
       </c>
       <c r="AN11" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="AO11">
-        <v>0.997271307400736</v>
+        <v>0.99680938221050552</v>
       </c>
       <c r="AP11">
-        <v>50.026030986507656</v>
+        <v>58.494659474065458</v>
       </c>
       <c r="AR11" t="s">
         <v>208</v>
@@ -5840,16 +5840,16 @@
         <v>213</v>
       </c>
       <c r="Y12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Z12" t="s">
         <v>250</v>
       </c>
       <c r="AA12">
-        <v>0.99760982224502215</v>
+        <v>0.99752858704396352</v>
       </c>
       <c r="AB12">
-        <v>43.819925507926904</v>
+        <v>45.309237527336073</v>
       </c>
       <c r="AD12" t="s">
         <v>208</v>
@@ -5879,13 +5879,13 @@
         <v>302</v>
       </c>
       <c r="AN12" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AO12">
-        <v>0.99783239241598654</v>
+        <v>0.99688151472382236</v>
       </c>
       <c r="AP12">
-        <v>39.739472373580618</v>
+        <v>57.172230063256528</v>
       </c>
       <c r="AR12" t="s">
         <v>208</v>
@@ -5918,10 +5918,10 @@
         <v>393</v>
       </c>
       <c r="BC12">
-        <v>0.99247871058903048</v>
+        <v>0.9890452551239991</v>
       </c>
       <c r="BD12">
-        <v>859.58960935239395</v>
+        <v>1033.0180098893456</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -5986,16 +5986,16 @@
         <v>215</v>
       </c>
       <c r="Y13" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="Z13" t="s">
         <v>251</v>
       </c>
       <c r="AA13">
-        <v>0.99787981106332757</v>
+        <v>0.99830959999082325</v>
       </c>
       <c r="AB13">
-        <v>38.870130505661258</v>
+        <v>30.990666834906836</v>
       </c>
       <c r="AD13" t="s">
         <v>208</v>
@@ -6025,13 +6025,13 @@
         <v>303</v>
       </c>
       <c r="AN13" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="AO13">
-        <v>0.99703956002650962</v>
+        <v>0.99903701836527781</v>
       </c>
       <c r="AP13">
-        <v>54.274732847322909</v>
+        <v>17.654663303240934</v>
       </c>
       <c r="AR13" t="s">
         <v>208</v>
@@ -6061,13 +6061,13 @@
         <v>394</v>
       </c>
       <c r="BB13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC13">
-        <v>0.99465658103727128</v>
+        <v>0.99204803562608146</v>
       </c>
       <c r="BD13">
-        <v>696.97528255040743</v>
+        <v>891.74667325258451</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6132,16 +6132,16 @@
         <v>217</v>
       </c>
       <c r="Y14" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="Z14" t="s">
         <v>252</v>
       </c>
       <c r="AA14">
-        <v>0.99680426739284655</v>
+        <v>0.99695219334663165</v>
       </c>
       <c r="AB14">
-        <v>58.588431131146443</v>
+        <v>55.876455311753809</v>
       </c>
       <c r="AD14" t="s">
         <v>208</v>
@@ -6171,13 +6171,13 @@
         <v>304</v>
       </c>
       <c r="AN14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO14">
-        <v>0.99791180040619776</v>
+        <v>0.99677372423705546</v>
       </c>
       <c r="AP14">
-        <v>38.283659219706969</v>
+        <v>59.148388987317084</v>
       </c>
       <c r="AR14" t="s">
         <v>208</v>
@@ -6207,13 +6207,13 @@
         <v>395</v>
       </c>
       <c r="BB14" t="s">
-        <v>258</v>
+        <v>396</v>
       </c>
       <c r="BC14">
-        <v>0.99802143263694565</v>
+        <v>0.98377193796342222</v>
       </c>
       <c r="BD14">
-        <v>445.73302977472883</v>
+        <v>1108.6022225242818</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -6278,16 +6278,16 @@
         <v>219</v>
       </c>
       <c r="Y15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Z15" t="s">
         <v>253</v>
       </c>
       <c r="AA15">
-        <v>0.99519981374862343</v>
+        <v>0.99714858208340607</v>
       </c>
       <c r="AB15">
-        <v>88.003414608570054</v>
+        <v>52.275995137556073</v>
       </c>
       <c r="AD15" t="s">
         <v>208</v>
@@ -6317,7 +6317,7 @@
         <v>305</v>
       </c>
       <c r="AN15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO15">
         <v>0.997538384460946</v>
@@ -6350,16 +6350,16 @@
         <v>326</v>
       </c>
       <c r="BA15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="BB15" t="s">
-        <v>397</v>
+        <v>250</v>
       </c>
       <c r="BC15">
-        <v>0.97995244062586495</v>
+        <v>0.98020088675493455</v>
       </c>
       <c r="BD15">
-        <v>1163.3483510292683</v>
+        <v>1159.7872898459386</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -6424,16 +6424,16 @@
         <v>221</v>
       </c>
       <c r="Y16" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s">
         <v>254</v>
       </c>
       <c r="AA16">
-        <v>0.99624499038466463</v>
+        <v>0.99676166859558202</v>
       </c>
       <c r="AB16">
-        <v>68.841842947814868</v>
+        <v>59.369409080996384</v>
       </c>
       <c r="AD16" t="s">
         <v>208</v>
@@ -6466,10 +6466,10 @@
         <v>257</v>
       </c>
       <c r="AO16">
-        <v>0.9988358690267034</v>
+        <v>0.99791180040619776</v>
       </c>
       <c r="AP16">
-        <v>21.342401177104485</v>
+        <v>38.283659219706969</v>
       </c>
       <c r="AR16" t="s">
         <v>208</v>
@@ -6499,13 +6499,13 @@
         <v>398</v>
       </c>
       <c r="BB16" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="BC16">
-        <v>0.97145281832041297</v>
+        <v>0.98708790481854047</v>
       </c>
       <c r="BD16">
-        <v>1285.1762707407468</v>
+        <v>1061.0733642675864</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -6570,16 +6570,16 @@
         <v>223</v>
       </c>
       <c r="Y17" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s">
         <v>255</v>
       </c>
       <c r="AA17">
-        <v>0.99751923210281201</v>
+        <v>0.99866273218910673</v>
       </c>
       <c r="AB17">
-        <v>45.480744781780636</v>
+        <v>24.516576533043679</v>
       </c>
       <c r="AD17" t="s">
         <v>208</v>
@@ -6612,10 +6612,10 @@
         <v>259</v>
       </c>
       <c r="AO17">
-        <v>0.99677372423705546</v>
+        <v>0.99669693410162119</v>
       </c>
       <c r="AP17">
-        <v>59.148388987317084</v>
+        <v>60.556208136943944</v>
       </c>
       <c r="AR17" t="s">
         <v>208</v>
@@ -6642,16 +6642,16 @@
         <v>330</v>
       </c>
       <c r="BA17" t="s">
+        <v>399</v>
+      </c>
+      <c r="BB17" t="s">
         <v>400</v>
       </c>
-      <c r="BB17" t="s">
-        <v>249</v>
-      </c>
       <c r="BC17">
-        <v>0.98020088675493455</v>
+        <v>0.98739755586167266</v>
       </c>
       <c r="BD17">
-        <v>1159.7872898459386</v>
+        <v>1056.635032649358</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -6716,16 +6716,16 @@
         <v>225</v>
       </c>
       <c r="Y18" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Z18" t="s">
         <v>256</v>
       </c>
       <c r="AA18">
-        <v>0.9963565402188086</v>
+        <v>0.99760982224502215</v>
       </c>
       <c r="AB18">
-        <v>66.796762655176224</v>
+        <v>43.819925507926904</v>
       </c>
       <c r="AD18" t="s">
         <v>208</v>
@@ -6755,13 +6755,13 @@
         <v>308</v>
       </c>
       <c r="AN18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AO18">
-        <v>0.99669693410162119</v>
+        <v>0.99587536861806769</v>
       </c>
       <c r="AP18">
-        <v>60.556208136943944</v>
+        <v>75.618242002091478</v>
       </c>
       <c r="AR18" t="s">
         <v>208</v>
@@ -6794,10 +6794,10 @@
         <v>402</v>
       </c>
       <c r="BC18">
-        <v>0.98377193796342222</v>
+        <v>0.99045604085294625</v>
       </c>
       <c r="BD18">
-        <v>1108.6022225242818</v>
+        <v>1010.6156163133485</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -6862,16 +6862,16 @@
         <v>227</v>
       </c>
       <c r="Y19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Z19" t="s">
         <v>257</v>
       </c>
       <c r="AA19">
-        <v>0.99864861119598014</v>
+        <v>0.99787981106332757</v>
       </c>
       <c r="AB19">
-        <v>24.775461407030388</v>
+        <v>38.870130505661258</v>
       </c>
       <c r="AD19" t="s">
         <v>208</v>
@@ -6901,13 +6901,13 @@
         <v>309</v>
       </c>
       <c r="AN19" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AO19">
-        <v>0.99587536861806769</v>
+        <v>0.997271307400736</v>
       </c>
       <c r="AP19">
-        <v>75.618242002091478</v>
+        <v>50.026030986507656</v>
       </c>
       <c r="AR19" t="s">
         <v>208</v>
@@ -6937,13 +6937,13 @@
         <v>403</v>
       </c>
       <c r="BB19" t="s">
-        <v>263</v>
+        <v>404</v>
       </c>
       <c r="BC19">
-        <v>0.99525173976906944</v>
+        <v>0.98547974671229588</v>
       </c>
       <c r="BD19">
-        <v>652.53676390947953</v>
+        <v>1084.1236304570925</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7008,16 +7008,16 @@
         <v>229</v>
       </c>
       <c r="Y20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Z20" t="s">
         <v>258</v>
       </c>
       <c r="AA20">
-        <v>0.99866273218910673</v>
+        <v>0.99680426739284655</v>
       </c>
       <c r="AB20">
-        <v>24.516576533043679</v>
+        <v>58.588431131146443</v>
       </c>
       <c r="AD20" t="s">
         <v>208</v>
@@ -7047,13 +7047,13 @@
         <v>310</v>
       </c>
       <c r="AN20" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="AO20">
-        <v>0.99519981374862343</v>
+        <v>0.99783239241598654</v>
       </c>
       <c r="AP20">
-        <v>88.003414608570054</v>
+        <v>39.739472373580618</v>
       </c>
       <c r="AR20" t="s">
         <v>208</v>
@@ -7080,16 +7080,16 @@
         <v>336</v>
       </c>
       <c r="BA20" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BB20" t="s">
-        <v>249</v>
+        <v>406</v>
       </c>
       <c r="BC20">
-        <v>0.99181181634249571</v>
+        <v>0.98880151660557103</v>
       </c>
       <c r="BD20">
-        <v>909.38437976031673</v>
+        <v>1036.511595320148</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7154,16 +7154,16 @@
         <v>231</v>
       </c>
       <c r="Y21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Z21" t="s">
         <v>259</v>
       </c>
       <c r="AA21">
-        <v>0.99695219334663165</v>
+        <v>0.99613015041875352</v>
       </c>
       <c r="AB21">
-        <v>55.876455311753809</v>
+        <v>70.94724232285219</v>
       </c>
       <c r="AD21" t="s">
         <v>208</v>
@@ -7193,13 +7193,13 @@
         <v>311</v>
       </c>
       <c r="AN21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AO21">
-        <v>0.99680938221050552</v>
+        <v>0.99703956002650962</v>
       </c>
       <c r="AP21">
-        <v>58.494659474065458</v>
+        <v>54.274732847322909</v>
       </c>
       <c r="AR21" t="s">
         <v>208</v>
@@ -7226,16 +7226,16 @@
         <v>338</v>
       </c>
       <c r="BA21" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="BB21" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BC21">
-        <v>0.99160189118519626</v>
+        <v>0.98756244444203367</v>
       </c>
       <c r="BD21">
-        <v>925.05879150534349</v>
+        <v>1054.2716296641843</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -7300,16 +7300,16 @@
         <v>233</v>
       </c>
       <c r="Y22" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="Z22" t="s">
         <v>260</v>
       </c>
       <c r="AA22">
-        <v>0.99714858208340607</v>
+        <v>0.99576560777715073</v>
       </c>
       <c r="AB22">
-        <v>52.275995137556073</v>
+        <v>77.630524085569377</v>
       </c>
       <c r="AD22" t="s">
         <v>208</v>
@@ -7339,13 +7339,13 @@
         <v>312</v>
       </c>
       <c r="AN22" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AO22">
-        <v>0.99688151472382236</v>
+        <v>0.99714892559180468</v>
       </c>
       <c r="AP22">
-        <v>57.172230063256528</v>
+        <v>52.269697483580167</v>
       </c>
       <c r="AR22" t="s">
         <v>208</v>
@@ -7372,16 +7372,16 @@
         <v>340</v>
       </c>
       <c r="BA22" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BB22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="BC22">
-        <v>0.99045604085294625</v>
+        <v>0.99044431412460865</v>
       </c>
       <c r="BD22">
-        <v>1010.6156163133485</v>
+        <v>1011.4912120292223</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -7488,10 +7488,10 @@
         <v>265</v>
       </c>
       <c r="AO23">
-        <v>0.99903701836527781</v>
+        <v>0.99624973186351284</v>
       </c>
       <c r="AP23">
-        <v>17.654663303240934</v>
+        <v>68.754915835597686</v>
       </c>
       <c r="AR23" t="s">
         <v>208</v>
@@ -7518,16 +7518,16 @@
         <v>342</v>
       </c>
       <c r="BA23" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="BB23" t="s">
-        <v>399</v>
+        <v>252</v>
       </c>
       <c r="BC23">
-        <v>0.98547974671229588</v>
+        <v>0.99453103995184811</v>
       </c>
       <c r="BD23">
-        <v>1084.1236304570925</v>
+        <v>706.34901692867311</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -7592,16 +7592,16 @@
         <v>237</v>
       </c>
       <c r="Y24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Z24" t="s">
         <v>262</v>
       </c>
       <c r="AA24">
-        <v>0.99613015041875352</v>
+        <v>0.9963565402188086</v>
       </c>
       <c r="AB24">
-        <v>70.94724232285219</v>
+        <v>66.796762655176224</v>
       </c>
       <c r="AD24" t="s">
         <v>208</v>
@@ -7631,13 +7631,13 @@
         <v>314</v>
       </c>
       <c r="AN24" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AO24">
-        <v>0.99714892559180468</v>
+        <v>0.9983148526184692</v>
       </c>
       <c r="AP24">
-        <v>52.269697483580167</v>
+        <v>30.894368661397099</v>
       </c>
       <c r="AR24" t="s">
         <v>208</v>
@@ -7664,16 +7664,16 @@
         <v>344</v>
       </c>
       <c r="BA24" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="BB24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BC24">
-        <v>0.98880151660557103</v>
+        <v>0.97800508983662982</v>
       </c>
       <c r="BD24">
-        <v>1036.511595320148</v>
+        <v>1191.2603790083058</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -7738,16 +7738,16 @@
         <v>239</v>
       </c>
       <c r="Y25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z25" t="s">
         <v>263</v>
       </c>
       <c r="AA25">
-        <v>0.99576560777715073</v>
+        <v>0.99864861119598014</v>
       </c>
       <c r="AB25">
-        <v>77.630524085569377</v>
+        <v>24.775461407030388</v>
       </c>
       <c r="AD25" t="s">
         <v>208</v>
@@ -7777,13 +7777,13 @@
         <v>315</v>
       </c>
       <c r="AN25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO25">
-        <v>0.99624973186351284</v>
+        <v>0.99875532250287602</v>
       </c>
       <c r="AP25">
-        <v>68.754915835597686</v>
+        <v>22.819087447272764</v>
       </c>
       <c r="AR25" t="s">
         <v>208</v>
@@ -7810,16 +7810,16 @@
         <v>346</v>
       </c>
       <c r="BA25" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BB25" t="s">
         <v>412</v>
       </c>
       <c r="BC25">
-        <v>0.9890452551239991</v>
+        <v>0.98869005479661864</v>
       </c>
       <c r="BD25">
-        <v>1033.0180098893456</v>
+        <v>1038.1092145818</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -7884,16 +7884,16 @@
         <v>241</v>
       </c>
       <c r="Y26" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="Z26" t="s">
         <v>264</v>
       </c>
       <c r="AA26">
-        <v>0.99676166859558202</v>
+        <v>0.99519981374862343</v>
       </c>
       <c r="AB26">
-        <v>59.369409080996384</v>
+        <v>88.003414608570054</v>
       </c>
       <c r="AD26" t="s">
         <v>208</v>
@@ -7923,13 +7923,13 @@
         <v>316</v>
       </c>
       <c r="AN26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AO26">
-        <v>0.9983148526184692</v>
+        <v>0.99519981374862343</v>
       </c>
       <c r="AP26">
-        <v>30.894368661397099</v>
+        <v>88.003414608570054</v>
       </c>
       <c r="AR26" t="s">
         <v>208</v>
@@ -7956,16 +7956,16 @@
         <v>348</v>
       </c>
       <c r="BA26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="BB26" t="s">
-        <v>260</v>
+        <v>415</v>
       </c>
       <c r="BC26">
-        <v>0.99204803562608146</v>
+        <v>0.99122598643981208</v>
       </c>
       <c r="BD26">
-        <v>891.74667325258451</v>
+        <v>953.12634582736666</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8030,16 +8030,16 @@
         <v>243</v>
       </c>
       <c r="Y27" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="Z27" t="s">
         <v>265</v>
       </c>
       <c r="AA27">
-        <v>0.99895498782328085</v>
+        <v>0.99624499038466463</v>
       </c>
       <c r="AB27">
-        <v>19.158556573184136</v>
+        <v>68.841842947814868</v>
       </c>
       <c r="AD27" t="s">
         <v>208</v>
@@ -8069,13 +8069,13 @@
         <v>317</v>
       </c>
       <c r="AN27" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AO27">
-        <v>0.99875532250287602</v>
+        <v>0.9988358690267034</v>
       </c>
       <c r="AP27">
-        <v>22.819087447272764</v>
+        <v>21.342401177104485</v>
       </c>
       <c r="AR27" t="s">
         <v>208</v>
@@ -8102,16 +8102,16 @@
         <v>350</v>
       </c>
       <c r="BA27" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="BB27" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="BC27">
-        <v>0.98756244444203367</v>
+        <v>0.97434200096433488</v>
       </c>
       <c r="BD27">
-        <v>1054.2716296641843</v>
+        <v>1243.7646528445334</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8176,16 +8176,16 @@
         <v>245</v>
       </c>
       <c r="Y28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z28" t="s">
         <v>266</v>
       </c>
       <c r="AA28">
-        <v>0.99830959999082325</v>
+        <v>0.99751923210281201</v>
       </c>
       <c r="AB28">
-        <v>30.990666834906836</v>
+        <v>45.480744781780636</v>
       </c>
       <c r="AR28" t="s">
         <v>208</v>
@@ -8212,16 +8212,16 @@
         <v>352</v>
       </c>
       <c r="BA28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="BB28" t="s">
-        <v>402</v>
+        <v>266</v>
       </c>
       <c r="BC28">
-        <v>0.99044431412460865</v>
+        <v>0.98426512774462438</v>
       </c>
       <c r="BD28">
-        <v>1011.4912120292223</v>
+        <v>1101.5331689937179</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8250,16 +8250,16 @@
         <v>354</v>
       </c>
       <c r="BA29" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="BB29" t="s">
-        <v>259</v>
+        <v>419</v>
       </c>
       <c r="BC29">
-        <v>0.99453103995184811</v>
+        <v>0.97856183821274934</v>
       </c>
       <c r="BD29">
-        <v>706.34901692867311</v>
+        <v>1183.280318950593</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8288,16 +8288,16 @@
         <v>356</v>
       </c>
       <c r="BA30" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="BB30" t="s">
-        <v>419</v>
+        <v>254</v>
       </c>
       <c r="BC30">
-        <v>0.97800508983662982</v>
+        <v>0.99877281687968489</v>
       </c>
       <c r="BD30">
-        <v>1191.2603790083058</v>
+        <v>389.62967298353118</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -8326,16 +8326,16 @@
         <v>358</v>
       </c>
       <c r="BA31" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="BB31" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="BC31">
-        <v>0.98869005479661864</v>
+        <v>0.9918697924155444</v>
       </c>
       <c r="BD31">
-        <v>1038.1092145818</v>
+        <v>905.05549963935277</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -8364,16 +8364,16 @@
         <v>360</v>
       </c>
       <c r="BA32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BB32" t="s">
-        <v>422</v>
+        <v>260</v>
       </c>
       <c r="BC32">
-        <v>0.99122598643981208</v>
+        <v>0.99525173976906944</v>
       </c>
       <c r="BD32">
-        <v>953.12634582736666</v>
+        <v>652.53676390947953</v>
       </c>
     </row>
     <row r="33" spans="44:56">
@@ -8402,16 +8402,16 @@
         <v>362</v>
       </c>
       <c r="BA33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="BB33" t="s">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="BC33">
-        <v>0.97856183821274934</v>
+        <v>0.99494925313382476</v>
       </c>
       <c r="BD33">
-        <v>1183.280318950593</v>
+        <v>675.12243267441886</v>
       </c>
     </row>
     <row r="34" spans="44:56">
@@ -8443,13 +8443,13 @@
         <v>425</v>
       </c>
       <c r="BB34" t="s">
-        <v>264</v>
+        <v>415</v>
       </c>
       <c r="BC34">
-        <v>0.99877281687968489</v>
+        <v>0.98361562599769714</v>
       </c>
       <c r="BD34">
-        <v>389.62967298353118</v>
+        <v>1110.8426940330071</v>
       </c>
     </row>
     <row r="35" spans="44:56">
@@ -8481,13 +8481,13 @@
         <v>426</v>
       </c>
       <c r="BB35" t="s">
-        <v>427</v>
+        <v>263</v>
       </c>
       <c r="BC35">
-        <v>0.9918697924155444</v>
+        <v>0.98974789112391137</v>
       </c>
       <c r="BD35">
-        <v>905.05549963935277</v>
+        <v>1022.9468938906032</v>
       </c>
     </row>
     <row r="36" spans="44:56">
@@ -8516,16 +8516,16 @@
         <v>368</v>
       </c>
       <c r="BA36" t="s">
+        <v>427</v>
+      </c>
+      <c r="BB36" t="s">
         <v>428</v>
       </c>
-      <c r="BB36" t="s">
-        <v>250</v>
-      </c>
       <c r="BC36">
-        <v>0.99494925313382476</v>
+        <v>0.97965413015263481</v>
       </c>
       <c r="BD36">
-        <v>675.12243267441886</v>
+        <v>1167.6241344789012</v>
       </c>
     </row>
     <row r="37" spans="44:56">
@@ -8557,13 +8557,13 @@
         <v>429</v>
       </c>
       <c r="BB37" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="BC37">
-        <v>0.98361562599769714</v>
+        <v>0.98774063701242087</v>
       </c>
       <c r="BD37">
-        <v>1110.8426940330071</v>
+        <v>1051.7175361553004</v>
       </c>
     </row>
     <row r="38" spans="44:56">
@@ -8592,16 +8592,16 @@
         <v>372</v>
       </c>
       <c r="BA38" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="BB38" t="s">
-        <v>257</v>
+        <v>432</v>
       </c>
       <c r="BC38">
-        <v>0.98974789112391137</v>
+        <v>0.98665471891556755</v>
       </c>
       <c r="BD38">
-        <v>1022.9468938906032</v>
+        <v>1067.2823622101978</v>
       </c>
     </row>
     <row r="39" spans="44:56">
@@ -8630,16 +8630,16 @@
         <v>374</v>
       </c>
       <c r="BA39" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="BB39" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="BC39">
-        <v>0.97965413015263481</v>
+        <v>0.9778696052684922</v>
       </c>
       <c r="BD39">
-        <v>1167.6241344789012</v>
+        <v>1193.2023244849449</v>
       </c>
     </row>
     <row r="40" spans="44:56">
@@ -8668,16 +8668,16 @@
         <v>376</v>
       </c>
       <c r="BA40" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="BB40" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="BC40">
-        <v>0.98774063701242087</v>
+        <v>0.99247871058903048</v>
       </c>
       <c r="BD40">
-        <v>1051.7175361553004</v>
+        <v>859.58960935239395</v>
       </c>
     </row>
     <row r="41" spans="44:56">
@@ -8706,16 +8706,16 @@
         <v>378</v>
       </c>
       <c r="BA41" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="BB41" t="s">
-        <v>436</v>
+        <v>257</v>
       </c>
       <c r="BC41">
-        <v>0.98665471891556755</v>
+        <v>0.99465658103727128</v>
       </c>
       <c r="BD41">
-        <v>1067.2823622101978</v>
+        <v>696.97528255040743</v>
       </c>
     </row>
     <row r="42" spans="44:56">
@@ -8747,13 +8747,13 @@
         <v>437</v>
       </c>
       <c r="BB42" t="s">
-        <v>410</v>
+        <v>250</v>
       </c>
       <c r="BC42">
-        <v>0.9778696052684922</v>
+        <v>0.99181181634249571</v>
       </c>
       <c r="BD42">
-        <v>1193.2023244849449</v>
+        <v>909.38437976031673</v>
       </c>
     </row>
     <row r="43" spans="44:56">
@@ -8785,13 +8785,13 @@
         <v>438</v>
       </c>
       <c r="BB43" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="BC43">
-        <v>0.98708790481854047</v>
+        <v>0.99160189118519626</v>
       </c>
       <c r="BD43">
-        <v>1061.0733642675864</v>
+        <v>925.05879150534349</v>
       </c>
     </row>
     <row r="44" spans="44:56">
@@ -8820,16 +8820,16 @@
         <v>384</v>
       </c>
       <c r="BA44" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="BB44" t="s">
-        <v>440</v>
+        <v>255</v>
       </c>
       <c r="BC44">
-        <v>0.98739755586167266</v>
+        <v>0.99802143263694565</v>
       </c>
       <c r="BD44">
-        <v>1056.635032649358</v>
+        <v>445.73302977472883</v>
       </c>
     </row>
     <row r="45" spans="44:56">
@@ -8861,13 +8861,13 @@
         <v>441</v>
       </c>
       <c r="BB45" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="BC45">
-        <v>0.97434200096433488</v>
+        <v>0.97995244062586495</v>
       </c>
       <c r="BD45">
-        <v>1243.7646528445334</v>
+        <v>1163.3483510292683</v>
       </c>
     </row>
     <row r="46" spans="44:56">
@@ -8899,13 +8899,13 @@
         <v>442</v>
       </c>
       <c r="BB46" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="BC46">
-        <v>0.98426512774462438</v>
+        <v>0.97145281832041297</v>
       </c>
       <c r="BD46">
-        <v>1101.5331689937179</v>
+        <v>1285.1762707407468</v>
       </c>
     </row>
   </sheetData>
@@ -8914,7 +8914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F862166-0F7F-405A-A949-BFC14FF847D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C15D6E5-D2C0-4222-BCF3-8DDF4C600B47}">
   <dimension ref="B9:Z46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9026,7 +9026,7 @@
         <v>443</v>
       </c>
       <c r="K11" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L11">
         <v>2.7638822400569127</v>
@@ -9059,7 +9059,7 @@
         <v>477</v>
       </c>
       <c r="X11" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Y11">
         <v>80.170500000000004</v>
@@ -9094,7 +9094,7 @@
         <v>445</v>
       </c>
       <c r="K12" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="L12">
         <v>20.77231157091439</v>
@@ -9127,7 +9127,7 @@
         <v>479</v>
       </c>
       <c r="X12" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="Y12">
         <v>44.241</v>
@@ -9162,7 +9162,7 @@
         <v>447</v>
       </c>
       <c r="K13" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="L13">
         <v>4.4741821578522556</v>
@@ -9195,7 +9195,7 @@
         <v>481</v>
       </c>
       <c r="X13" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="Y13">
         <v>12.216749999999999</v>
@@ -9230,7 +9230,7 @@
         <v>449</v>
       </c>
       <c r="K14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L14">
         <v>13.277020846906277</v>
@@ -9263,7 +9263,7 @@
         <v>483</v>
       </c>
       <c r="X14" t="s">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="Y14">
         <v>10.0815</v>
@@ -9298,7 +9298,7 @@
         <v>451</v>
       </c>
       <c r="K15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L15">
         <v>12.558088674500979</v>
@@ -9331,7 +9331,7 @@
         <v>485</v>
       </c>
       <c r="X15" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="Y15">
         <v>86.578500000000005</v>
@@ -9399,7 +9399,7 @@
         <v>487</v>
       </c>
       <c r="X16" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="Y16">
         <v>99.012749999999997</v>
@@ -9434,7 +9434,7 @@
         <v>455</v>
       </c>
       <c r="K17" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L17">
         <v>4.395901085454879</v>
@@ -9502,7 +9502,7 @@
         <v>457</v>
       </c>
       <c r="K18" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L18">
         <v>14.819127585736313</v>
@@ -9535,7 +9535,7 @@
         <v>491</v>
       </c>
       <c r="X18" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="Y18">
         <v>114.90600000000001</v>
@@ -9570,7 +9570,7 @@
         <v>459</v>
       </c>
       <c r="K19" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="L19">
         <v>14.555843490090952</v>
@@ -9603,7 +9603,7 @@
         <v>493</v>
       </c>
       <c r="X19" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="Y19">
         <v>137.93549999999999</v>
@@ -9638,7 +9638,7 @@
         <v>461</v>
       </c>
       <c r="K20" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="L20">
         <v>0.58308420099592573</v>
@@ -9671,7 +9671,7 @@
         <v>495</v>
       </c>
       <c r="X20" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
       <c r="Y20">
         <v>103.48950000000001</v>
@@ -9706,7 +9706,7 @@
         <v>463</v>
       </c>
       <c r="K21" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="L21">
         <v>14.178109781380291</v>
@@ -9739,7 +9739,7 @@
         <v>497</v>
       </c>
       <c r="X21" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="Y21">
         <v>86.1815</v>
@@ -9774,7 +9774,7 @@
         <v>465</v>
       </c>
       <c r="K22" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="L22">
         <v>16.555830372654277</v>
@@ -9807,7 +9807,7 @@
         <v>499</v>
       </c>
       <c r="X22" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="Y22">
         <v>59.469000000000001</v>
@@ -9842,7 +9842,7 @@
         <v>467</v>
       </c>
       <c r="K23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L23">
         <v>8.4231349606719377</v>
@@ -9875,7 +9875,7 @@
         <v>501</v>
       </c>
       <c r="X23" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="Y23">
         <v>18.631499999999999</v>
@@ -9910,7 +9910,7 @@
         <v>469</v>
       </c>
       <c r="K24" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L24">
         <v>9.7350817832941772</v>
@@ -9943,7 +9943,7 @@
         <v>503</v>
       </c>
       <c r="X24" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="Y24">
         <v>50.616750000000003</v>
@@ -9978,7 +9978,7 @@
         <v>471</v>
       </c>
       <c r="K25" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L25">
         <v>6.6947392871568727</v>
@@ -10011,7 +10011,7 @@
         <v>505</v>
       </c>
       <c r="X25" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="Y25">
         <v>86.505250000000004</v>
@@ -10046,7 +10046,7 @@
         <v>473</v>
       </c>
       <c r="K26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L26">
         <v>20.575257283369904</v>
@@ -10079,7 +10079,7 @@
         <v>507</v>
       </c>
       <c r="X26" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="Y26">
         <v>123.74475</v>
@@ -10114,7 +10114,7 @@
         <v>475</v>
       </c>
       <c r="K27" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="L27">
         <v>3.7041201064940852</v>
@@ -10147,7 +10147,7 @@
         <v>509</v>
       </c>
       <c r="X27" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="Y27">
         <v>37.392000000000003</v>
@@ -10182,7 +10182,7 @@
         <v>511</v>
       </c>
       <c r="X28" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="Y28">
         <v>9.8302499999999995</v>
@@ -10217,7 +10217,7 @@
         <v>513</v>
       </c>
       <c r="X29" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="Y29">
         <v>123.97125</v>
@@ -10252,7 +10252,7 @@
         <v>515</v>
       </c>
       <c r="X30" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="Y30">
         <v>2.5499999999999998E-2</v>
@@ -10287,7 +10287,7 @@
         <v>517</v>
       </c>
       <c r="X31" t="s">
-        <v>395</v>
+        <v>440</v>
       </c>
       <c r="Y31">
         <v>2.3452500000000001</v>
@@ -10322,7 +10322,7 @@
         <v>519</v>
       </c>
       <c r="X32" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="Y32">
         <v>91.364249999999998</v>
@@ -10357,7 +10357,7 @@
         <v>521</v>
       </c>
       <c r="X33" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="Y33">
         <v>95.313000000000002</v>
@@ -10392,7 +10392,7 @@
         <v>523</v>
       </c>
       <c r="X34" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="Y34">
         <v>12.18525</v>
@@ -10427,7 +10427,7 @@
         <v>525</v>
       </c>
       <c r="X35" t="s">
-        <v>396</v>
+        <v>441</v>
       </c>
       <c r="Y35">
         <v>348.49275</v>
@@ -10462,7 +10462,7 @@
         <v>527</v>
       </c>
       <c r="X36" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="Y36">
         <v>60.109499999999997</v>
@@ -10497,7 +10497,7 @@
         <v>529</v>
       </c>
       <c r="X37" t="s">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="Y37">
         <v>27.159749999999999</v>
@@ -10532,7 +10532,7 @@
         <v>531</v>
       </c>
       <c r="X38" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="Y38">
         <v>7.056</v>
@@ -10567,7 +10567,7 @@
         <v>533</v>
       </c>
       <c r="X39" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="Y39">
         <v>149.28225</v>
@@ -10602,7 +10602,7 @@
         <v>535</v>
       </c>
       <c r="X40" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="Y40">
         <v>6.8767500000000004</v>
@@ -10637,7 +10637,7 @@
         <v>537</v>
       </c>
       <c r="X41" t="s">
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="Y41">
         <v>214.62975</v>
@@ -10672,7 +10672,7 @@
         <v>539</v>
       </c>
       <c r="X42" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="Y42">
         <v>198.0975</v>
@@ -10707,7 +10707,7 @@
         <v>541</v>
       </c>
       <c r="X43" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="Y43">
         <v>9.0314999999999994</v>
@@ -10742,7 +10742,7 @@
         <v>543</v>
       </c>
       <c r="X44" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="Y44">
         <v>107.901</v>
@@ -10777,7 +10777,7 @@
         <v>545</v>
       </c>
       <c r="X45" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="Y45">
         <v>298.90275000000003</v>
@@ -10812,7 +10812,7 @@
         <v>547</v>
       </c>
       <c r="X46" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="Y46">
         <v>102.336</v>
@@ -10827,7 +10827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403BD560-E652-4567-B9CE-0D8F3D402A50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3366A813-6AF7-4A3C-AC24-62D4D20BBB28}">
   <dimension ref="B9:Y151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
